--- a/docs/reports/태양광·수소 데이터수집·AI분석 예상안.xlsx
+++ b/docs/reports/태양광·수소 데이터수집·AI분석 예상안.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jungm\Desktop\projects\simple\solar-dashboard\docs\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832C9391-4A2C-43D7-A0FB-D3654CA9CBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9424E424-1E74-4618-A110-2F189751A6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9713" uniqueCount="5833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9713" uniqueCount="5831">
   <si>
     <t>이 워크북 읽는 법</t>
   </si>
@@ -16787,7 +16787,7 @@
     <t>LS-102</t>
   </si>
   <si>
-    <t>ELZ1/WTU1/TANK1 · high  — B.4 감압·버퍼 — 수소 재고 환산과 조정기 시트 누설 판정</t>
+    <t>ELZ1/WTU1/TANK1 · high</t>
   </si>
   <si>
     <t>PDT-101</t>
@@ -16862,7 +16862,7 @@
     <t>XV-402</t>
   </si>
   <si>
-    <t>O2P1/LOAD1 · o2.loading  — B.2 폐열회수 HX-301 — 교차누설로부터 수전해 스택을 지키는 것이 먼저다</t>
+    <t>O2P1/LOAD1 · o2.loading</t>
   </si>
   <si>
     <t>미지정</t>
@@ -16958,9 +16958,6 @@
     <t>열교환기 2차측 차압 [hx.pressure.diff.cold]</t>
   </si>
   <si>
-    <t>FC1/HX1  — B.3 수처리 — 물수지 폐합과 소모품 상태 기반 관리</t>
-  </si>
-  <si>
     <t>TT-202</t>
   </si>
   <si>
@@ -16971,9 +16968,6 @@
   </si>
   <si>
     <t>방출관 온도 [vent.temp]</t>
-  </si>
-  <si>
-    <t>PRV1  — B.5 외부 수소 반입 — 이것이 없으면 물질수지 식 자체가 성립하지 않는다</t>
   </si>
   <si>
     <t>펌프 소비전력 [pump.power]</t>
@@ -40342,7 +40336,7 @@
         <v>5468</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>5469</v>
+        <v>5317</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>398</v>
@@ -40356,13 +40350,13 @@
         <v>5366</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>5470</v>
+        <v>5469</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>5424</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>5471</v>
+        <v>5470</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>999</v>
@@ -40376,13 +40370,13 @@
         <v>5366</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>5471</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>5472</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>5473</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>5474</v>
+        <v>5312</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>999</v>
@@ -40399,10 +40393,10 @@
         <v>5438</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>5475</v>
+        <v>5473</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>5476</v>
+        <v>5474</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>1007</v>
@@ -40419,10 +40413,10 @@
         <v>5438</v>
       </c>
       <c r="C86" s="4" t="s">
+        <v>5473</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>5475</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>5477</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>1007</v>
@@ -40439,7 +40433,7 @@
         <v>5438</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>5475</v>
+        <v>5473</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>5381</v>
@@ -40480,12 +40474,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5478</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>5479</v>
+        <v>5477</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -40505,22 +40499,22 @@
         <v>3017</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>5478</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5479</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>5480</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>5481</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>5482</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>5483</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>5484</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>5485</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>29</v>
@@ -40531,25 +40525,25 @@
         <v>51</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>5484</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5485</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>5486</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>5487</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>5488</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>5489</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="6" t="s">
         <v>5490</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>5492</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40557,25 +40551,25 @@
         <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>5491</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>5492</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>5493</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>5494</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>5495</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>5496</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>5497</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>5498</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40583,25 +40577,25 @@
         <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>5497</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>5498</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>5499</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>5500</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>5501</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>5502</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>5503</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>5491</v>
+        <v>5489</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>5492</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="38.25" x14ac:dyDescent="0.3">
@@ -40609,25 +40603,25 @@
         <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>5502</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>5503</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>5504</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>5505</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>5506</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>5507</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>5508</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>5509</v>
-      </c>
       <c r="H9" s="6" t="s">
-        <v>5492</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40635,25 +40629,25 @@
         <v>51</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>5508</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5509</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>5510</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>5511</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>5512</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="G10" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>5513</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>5514</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>5515</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40661,25 +40655,25 @@
         <v>51</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>5514</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>5515</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>5516</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>5517</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>5518</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>5519</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="6" t="s">
         <v>5520</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>5521</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>5522</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -40687,25 +40681,25 @@
         <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>5521</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>5522</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>5523</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>5524</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>5525</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>5526</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>5527</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>5521</v>
+        <v>5519</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>5492</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -40713,25 +40707,25 @@
         <v>51</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>5526</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>5527</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>5528</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>5529</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>5530</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>5531</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>5532</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>5509</v>
+        <v>5507</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>5492</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="38.25" x14ac:dyDescent="0.3">
@@ -40739,25 +40733,25 @@
         <v>51</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>5531</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>5532</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>5533</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>5534</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>5535</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>5536</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>5537</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>5538</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="38.25" x14ac:dyDescent="0.3">
@@ -40765,25 +40759,25 @@
         <v>51</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>5537</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>5538</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>5539</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>5540</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>5541</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>5542</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>5543</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>5509</v>
+        <v>5507</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>5498</v>
+        <v>5496</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40791,25 +40785,25 @@
         <v>52</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>5542</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>5543</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>5544</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>5545</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>5546</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="G16" s="6" t="s">
+        <v>5519</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>5547</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>5548</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>5521</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>5549</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="102" x14ac:dyDescent="0.3">
@@ -40817,25 +40811,25 @@
         <v>52</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>5548</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>5549</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>5550</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>5551</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>5552</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="G17" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>5553</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>5554</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>5555</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40843,25 +40837,25 @@
         <v>52</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>5554</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>5555</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>5556</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>5557</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>5558</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="G18" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>5559</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>5560</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>5561</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -40869,25 +40863,25 @@
         <v>52</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>5560</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>5561</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>5562</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>5563</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>5564</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="G19" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>5565</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>5566</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>5567</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="114.75" x14ac:dyDescent="0.3">
@@ -40895,25 +40889,25 @@
         <v>52</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>5566</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>5567</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>5568</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>5569</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>5570</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="G20" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>5571</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>5572</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>5573</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40921,25 +40915,25 @@
         <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>5572</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>5573</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>5574</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>5575</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>5576</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="G21" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>5577</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>5578</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>5579</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40947,25 +40941,25 @@
         <v>52</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>5578</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>5579</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>5580</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>5581</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>5582</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="G22" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>5583</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>5584</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>5585</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -40973,25 +40967,25 @@
         <v>52</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>5584</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>5585</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>5586</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>5587</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>5588</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="G23" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>5589</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>5590</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>5591</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -40999,25 +40993,25 @@
         <v>52</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>5590</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>5591</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>5592</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>5593</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>5594</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="G24" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>5595</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>5596</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>5597</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41025,25 +41019,25 @@
         <v>52</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>5596</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>5597</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>5598</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>5599</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>5600</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="G25" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>5601</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>5602</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>5603</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41051,25 +41045,25 @@
         <v>53</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>5602</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>5603</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>5604</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>5605</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>5606</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="G26" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>5607</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>5608</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>5609</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41077,25 +41071,25 @@
         <v>53</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>5608</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>5609</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>5610</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>5611</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>5612</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="G27" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>5613</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>5614</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>5615</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41103,25 +41097,25 @@
         <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>5614</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>5615</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>5616</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>5617</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>5618</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="G28" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>5619</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>5620</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>5621</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41129,25 +41123,25 @@
         <v>53</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>5620</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>5621</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>5622</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>5623</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>5624</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="G29" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>5625</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>5626</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>5627</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41155,25 +41149,25 @@
         <v>53</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>5626</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>5627</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>5628</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>5629</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>5630</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="G30" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>5631</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>5632</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>5633</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41181,25 +41175,25 @@
         <v>53</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>5632</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>5633</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>5634</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>5635</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="F31" s="4" t="s">
         <v>5636</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="G31" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>5637</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>5638</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>5639</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41207,25 +41201,25 @@
         <v>53</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>5638</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>5639</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>5640</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>5641</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>5642</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="G32" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>5643</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>5644</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>5645</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41233,25 +41227,25 @@
         <v>53</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>5644</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>5645</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>5646</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>5647</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>5648</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>5649</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="H33" s="6" t="s">
         <v>5650</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>5651</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>5652</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41259,25 +41253,25 @@
         <v>53</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>5651</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>5652</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>5653</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>5654</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>5655</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="G34" s="6" t="s">
+        <v>5649</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>5656</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>5657</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>5651</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>5658</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41285,25 +41279,25 @@
         <v>53</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>5657</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>5658</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>5659</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>5660</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>5661</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="G35" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>5662</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>5663</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>5664</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41311,25 +41305,25 @@
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>5663</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>5664</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>5665</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>5666</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>5667</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="G36" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>5668</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>5669</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>5670</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41337,25 +41331,25 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>5669</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>5670</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>5671</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>5672</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>5673</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="G37" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>5674</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>5675</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>5676</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41363,25 +41357,25 @@
         <v>53</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>5675</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>5676</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>5677</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>5678</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>5679</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="G38" s="6" t="s">
+        <v>5649</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>5680</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>5681</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>5651</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>5682</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -41389,25 +41383,25 @@
         <v>54</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>5681</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>5682</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>5683</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>5684</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>5685</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="G39" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>5686</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>5687</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>5688</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41415,25 +41409,25 @@
         <v>54</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>5687</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>5688</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>5689</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>5690</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>5691</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="G40" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>5692</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>5693</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>5694</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41441,25 +41435,25 @@
         <v>54</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>5693</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>5694</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>5695</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>5696</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="F41" s="4" t="s">
         <v>5697</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="G41" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>5698</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>5699</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>5700</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41467,25 +41461,25 @@
         <v>54</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>5699</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>5700</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>5701</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>5702</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>5703</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="G42" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>5704</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>5705</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>5706</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41493,25 +41487,25 @@
         <v>54</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>5705</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>5706</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>5707</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>5708</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>5709</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="G43" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>5710</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>5711</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>5712</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="102" x14ac:dyDescent="0.3">
@@ -41519,25 +41513,25 @@
         <v>54</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>5711</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>5712</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>5713</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>5714</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>5715</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="G44" s="6" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>5716</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>5717</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>5491</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>5718</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41545,25 +41539,25 @@
         <v>54</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>5717</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>5718</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>5719</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>5720</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>5721</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="G45" s="6" t="s">
+        <v>5519</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>5722</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>5723</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>5521</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>5724</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41571,25 +41565,25 @@
         <v>54</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>5723</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>5724</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>5725</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>5726</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>5727</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="G46" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>5728</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>5729</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>5730</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41597,25 +41591,25 @@
         <v>54</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>5729</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>5730</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>5731</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>5732</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>5733</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="G47" s="6" t="s">
+        <v>5519</v>
+      </c>
+      <c r="H47" s="6" t="s">
         <v>5734</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>5735</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>5521</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>5736</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41623,25 +41617,25 @@
         <v>54</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>5735</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>5736</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>5737</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>5738</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>5739</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="G48" s="6" t="s">
+        <v>5507</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>5740</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>5741</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>5509</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>5742</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41649,25 +41643,25 @@
         <v>55</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>5741</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>5742</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>5743</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>5744</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>5745</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>5746</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>5747</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>5748</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="127.5" x14ac:dyDescent="0.3">
@@ -41675,25 +41669,25 @@
         <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>5747</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>5748</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>5749</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>5750</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>5751</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>5752</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>5753</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>5754</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="153" x14ac:dyDescent="0.3">
@@ -41701,25 +41695,25 @@
         <v>55</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>5753</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>5754</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>5755</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>5756</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="F51" s="4" t="s">
         <v>5757</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>5758</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>5759</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>5760</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
@@ -41727,25 +41721,25 @@
         <v>55</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>5759</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>5760</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>5761</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>5762</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>5763</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>5764</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>5765</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>5766</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="178.5" x14ac:dyDescent="0.3">
@@ -41753,25 +41747,25 @@
         <v>55</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>5765</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>5766</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>5767</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>5768</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>5769</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>5770</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>5771</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>5772</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -41779,25 +41773,25 @@
         <v>55</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>5771</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>5772</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>5773</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>5774</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>5775</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>5776</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>5777</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>5778</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41805,25 +41799,25 @@
         <v>55</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>5777</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>5778</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>5779</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>5780</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>5781</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>5782</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>5783</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>5784</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
@@ -41831,25 +41825,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>5783</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>5784</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>5785</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="E56" s="4" t="s">
         <v>5786</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="F56" s="4" t="s">
         <v>5787</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>5788</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>5789</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>5790</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41857,25 +41851,25 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>5789</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>5790</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>5791</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="E57" s="4" t="s">
         <v>5792</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="F57" s="4" t="s">
         <v>5793</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>5794</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>5795</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>5796</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="102" x14ac:dyDescent="0.3">
@@ -41883,25 +41877,25 @@
         <v>55</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>5795</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>5796</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>5797</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>5798</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>5799</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>5800</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>5801</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>4234</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>5802</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="114.75" x14ac:dyDescent="0.3">
@@ -41909,25 +41903,25 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>5801</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>5802</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>5803</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="E59" s="4" t="s">
         <v>5804</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="F59" s="4" t="s">
         <v>5805</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>5806</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>5807</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>5808</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="127.5" x14ac:dyDescent="0.3">
@@ -41935,25 +41929,25 @@
         <v>55</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>5807</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>5808</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>5809</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="E60" s="4" t="s">
         <v>5810</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>5811</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>5812</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>5813</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>5814</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41961,25 +41955,25 @@
         <v>55</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>5813</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>5814</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>5815</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>5816</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>5817</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>5818</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>5819</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>5820</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="127.5" x14ac:dyDescent="0.3">
@@ -41987,25 +41981,25 @@
         <v>55</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>5819</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>5820</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>5821</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>5822</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>5823</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>5824</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>5825</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>5826</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -42013,25 +42007,25 @@
         <v>55</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>5825</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>5826</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>5827</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>5828</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>5829</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>5830</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>5831</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>5832</v>
+        <v>5830</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reports/태양광·수소 데이터수집·AI분석 예상안.xlsx
+++ b/docs/reports/태양광·수소 데이터수집·AI분석 예상안.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jungm\Desktop\projects\simple\solar-dashboard\docs\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9424E424-1E74-4618-A110-2F189751A6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FA6A50-84C5-4785-B2B8-EE8E9E0D4A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,15 +62,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9713" uniqueCount="5831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9719" uniqueCount="5832">
   <si>
     <t>이 워크북 읽는 법</t>
   </si>
   <si>
-    <t>실제 원시데이터가 없는 상태에서 업계 표준·공공기관·제조사 자료를 근거로 만든 예상안입니다. 수치는 출처 기준이며 설비 사양이 정해지면 다시 확인해야 합니다. 제2판(2026-09-17)에서 실제 사업 도면(가평 2MW 청정수소발전 P&amp;ID, FCND-GP-PID-002 REV.2) 적용 결과를 더했습니다. 초판 2026-09-14.</t>
-  </si>
-  <si>
-    <t>주식회사 퍼스트씨앤디 · 작성일 2026. 09. 17</t>
+    <t>실제 원시데이터가 없는 상태에서 업계 표준·공공기관·제조사 자료를 근거로 만든 예상안입니다. 수치는 출처 기준이며 설비 사양이 정해지면 다시 확인해야 합니다. 제2판(2026-09-17)에서 실제 사업 도면(가평 2MW 청정수소발전 P&amp;ID, FCND-GP-PID-002 REV.2) 적용 결과를 더했고, 제3판(2026-09-22)에서 전해조 퍼지 카운터를 신설 요청 목록에 더했습니다. 초판 2026-09-14.</t>
+  </si>
+  <si>
+    <t>주식회사 퍼스트씨앤디 · 작성일 2026. 09. 22</t>
   </si>
   <si>
     <t>시트</t>
@@ -16397,7 +16397,7 @@
     <t>가평 2MW 청정수소발전 — 도면 적용 결과 (FCND-GP-PID-002 REV.2)</t>
   </si>
   <si>
-    <t>고객사가 보낸 실제 사업 도면을 그대로 넣은 결과입니다. 설비 17개를 도면 명판대로 등록했고, 계장 태그 10점은 계측 항목에 바로 매핑했으며, 나머지 52행(필수 37·권장 15)은 미설치라 데이터 계약 요청 목록이 됩니다. 명판의 '미확인'은 추정값으로 채우지 않고 그대로 남긴 값이며, 그 자체가 벤더·설계사 회신 대기 목록입니다.</t>
+    <t>고객사가 보낸 실제 사업 도면을 그대로 넣은 결과입니다. 설비 17개를 도면 명판대로 등록했고, 계장 태그 10점은 계측 항목에 바로 매핑했으며, 나머지 53행(필수 37·권장 16)은 미설치라 데이터 계약 요청 목록이 됩니다. 명판의 '미확인'은 추정값으로 채우지 않고 그대로 남긴 값이며, 그 자체가 벤더·설계사 회신 대기 목록입니다.</t>
   </si>
   <si>
     <t>코드·태그</t>
@@ -16977,6 +16977,9 @@
   </si>
   <si>
     <t>ELZ1/WTU1 · loop</t>
+  </si>
+  <si>
+    <t>퍼지 횟수(누적) [purge.count]</t>
   </si>
   <si>
     <t>부속 계통 다섯 갈래의 고장 모드와 오탐 함정</t>
@@ -38790,7 +38793,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -40442,6 +40445,26 @@
         <v>1007</v>
       </c>
       <c r="F87" s="6" t="s">
+        <v>5450</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="6" t="s">
+        <v>5366</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>5438</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>5476</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>5297</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="F88" s="6" t="s">
         <v>5450</v>
       </c>
     </row>
@@ -40474,12 +40497,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5476</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>5477</v>
+        <v>5478</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -40499,22 +40522,22 @@
         <v>3017</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5478</v>
+        <v>5479</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>5479</v>
+        <v>5480</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>5480</v>
+        <v>5481</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>5481</v>
+        <v>5482</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>5482</v>
+        <v>5483</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>5483</v>
+        <v>5484</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>29</v>
@@ -40525,25 +40548,25 @@
         <v>51</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5484</v>
+        <v>5485</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>5485</v>
+        <v>5486</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>5486</v>
+        <v>5487</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>5487</v>
+        <v>5488</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>5488</v>
+        <v>5489</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40551,25 +40574,25 @@
         <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5491</v>
+        <v>5492</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>5494</v>
+        <v>5495</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>5495</v>
+        <v>5496</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>5496</v>
+        <v>5497</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40577,25 +40600,25 @@
         <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>5498</v>
+        <v>5499</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>5499</v>
+        <v>5500</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>5500</v>
+        <v>5501</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>5501</v>
+        <v>5502</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="38.25" x14ac:dyDescent="0.3">
@@ -40603,25 +40626,25 @@
         <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>5502</v>
+        <v>5503</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>5503</v>
+        <v>5504</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>5504</v>
+        <v>5505</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>5505</v>
+        <v>5506</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40629,25 +40652,25 @@
         <v>51</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>5509</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5510</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>5511</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>5512</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>5513</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>5508</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>5509</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>5510</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>5511</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>5512</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>5507</v>
-      </c>
       <c r="H10" s="6" t="s">
-        <v>5513</v>
+        <v>5514</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40655,25 +40678,25 @@
         <v>51</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>5514</v>
+        <v>5515</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>5515</v>
+        <v>5516</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>5516</v>
+        <v>5517</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>5517</v>
+        <v>5518</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>5520</v>
+        <v>5521</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -40681,25 +40704,25 @@
         <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>5521</v>
+        <v>5522</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>5522</v>
+        <v>5523</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>5523</v>
+        <v>5524</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>5524</v>
+        <v>5525</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>5525</v>
+        <v>5526</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -40707,25 +40730,25 @@
         <v>51</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>5526</v>
+        <v>5527</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>5527</v>
+        <v>5528</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>5528</v>
+        <v>5529</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="38.25" x14ac:dyDescent="0.3">
@@ -40733,25 +40756,25 @@
         <v>51</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>5532</v>
+        <v>5533</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>5533</v>
+        <v>5534</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>5535</v>
+        <v>5536</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>5536</v>
+        <v>5537</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="38.25" x14ac:dyDescent="0.3">
@@ -40759,25 +40782,25 @@
         <v>51</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>5537</v>
+        <v>5538</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>5538</v>
+        <v>5539</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>5539</v>
+        <v>5540</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>5540</v>
+        <v>5541</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>5541</v>
+        <v>5542</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>5496</v>
+        <v>5497</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40785,25 +40808,25 @@
         <v>52</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>5542</v>
+        <v>5543</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>5543</v>
+        <v>5544</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>5545</v>
+        <v>5546</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>5547</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="102" x14ac:dyDescent="0.3">
@@ -40811,25 +40834,25 @@
         <v>52</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>5548</v>
+        <v>5549</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>5550</v>
+        <v>5551</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>5551</v>
+        <v>5552</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>5552</v>
+        <v>5553</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>5553</v>
+        <v>5554</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40837,25 +40860,25 @@
         <v>52</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>5555</v>
+        <v>5556</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>5557</v>
+        <v>5558</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>5559</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -40863,25 +40886,25 @@
         <v>52</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>5562</v>
+        <v>5563</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>5563</v>
+        <v>5564</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>5564</v>
+        <v>5565</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>5565</v>
+        <v>5566</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="114.75" x14ac:dyDescent="0.3">
@@ -40889,25 +40912,25 @@
         <v>52</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>5566</v>
+        <v>5567</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>5568</v>
+        <v>5569</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>5570</v>
+        <v>5571</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>5571</v>
+        <v>5572</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -40915,25 +40938,25 @@
         <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>5572</v>
+        <v>5573</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>5574</v>
+        <v>5575</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>5575</v>
+        <v>5576</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>5576</v>
+        <v>5577</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>5577</v>
+        <v>5578</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -40941,25 +40964,25 @@
         <v>52</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>5578</v>
+        <v>5579</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>5579</v>
+        <v>5580</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>5581</v>
+        <v>5582</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>5582</v>
+        <v>5583</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>5583</v>
+        <v>5584</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -40967,25 +40990,25 @@
         <v>52</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>5584</v>
+        <v>5585</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>5585</v>
+        <v>5586</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>5586</v>
+        <v>5587</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>5587</v>
+        <v>5588</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>5588</v>
+        <v>5589</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>5589</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -40993,25 +41016,25 @@
         <v>52</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>5590</v>
+        <v>5591</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>5591</v>
+        <v>5592</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>5592</v>
+        <v>5593</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>5593</v>
+        <v>5594</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>5594</v>
+        <v>5595</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>5595</v>
+        <v>5596</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41019,25 +41042,25 @@
         <v>52</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>5596</v>
+        <v>5597</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>5597</v>
+        <v>5598</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>5598</v>
+        <v>5599</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>5599</v>
+        <v>5600</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>5600</v>
+        <v>5601</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>5601</v>
+        <v>5602</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41045,25 +41068,25 @@
         <v>53</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>5602</v>
+        <v>5603</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>5603</v>
+        <v>5604</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>5604</v>
+        <v>5605</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>5607</v>
+        <v>5608</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41071,25 +41094,25 @@
         <v>53</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>5608</v>
+        <v>5609</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41097,25 +41120,25 @@
         <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>5616</v>
+        <v>5617</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>5617</v>
+        <v>5618</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41123,25 +41146,25 @@
         <v>53</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>5623</v>
+        <v>5624</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>5625</v>
+        <v>5626</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41149,25 +41172,25 @@
         <v>53</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41175,25 +41198,25 @@
         <v>53</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>5634</v>
+        <v>5635</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>5637</v>
+        <v>5638</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41201,25 +41224,25 @@
         <v>53</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>5638</v>
+        <v>5639</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>5640</v>
+        <v>5641</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>5641</v>
+        <v>5642</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>5642</v>
+        <v>5643</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>5643</v>
+        <v>5644</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41227,25 +41250,25 @@
         <v>53</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>5644</v>
+        <v>5645</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>5647</v>
+        <v>5648</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>5648</v>
+        <v>5649</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>5650</v>
+        <v>5651</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41253,25 +41276,25 @@
         <v>53</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>5651</v>
+        <v>5652</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>5652</v>
+        <v>5653</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>5653</v>
+        <v>5654</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>5654</v>
+        <v>5655</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>5655</v>
+        <v>5656</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>5656</v>
+        <v>5657</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41279,25 +41302,25 @@
         <v>53</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>5657</v>
+        <v>5658</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>5658</v>
+        <v>5659</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>5659</v>
+        <v>5660</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>5662</v>
+        <v>5663</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41305,25 +41328,25 @@
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>5663</v>
+        <v>5664</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>5665</v>
+        <v>5666</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>5666</v>
+        <v>5667</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>5667</v>
+        <v>5668</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>5668</v>
+        <v>5669</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41331,25 +41354,25 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>5669</v>
+        <v>5670</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>5670</v>
+        <v>5671</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>5671</v>
+        <v>5672</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>5672</v>
+        <v>5673</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>5673</v>
+        <v>5674</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>5674</v>
+        <v>5675</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41357,25 +41380,25 @@
         <v>53</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>5675</v>
+        <v>5676</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>5677</v>
+        <v>5678</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>5678</v>
+        <v>5679</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>5679</v>
+        <v>5680</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>5680</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -41383,25 +41406,25 @@
         <v>54</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>5682</v>
+        <v>5683</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>5683</v>
+        <v>5684</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>5686</v>
+        <v>5687</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41409,25 +41432,25 @@
         <v>54</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>5687</v>
+        <v>5688</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>5688</v>
+        <v>5689</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>5691</v>
+        <v>5692</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>5692</v>
+        <v>5693</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41435,25 +41458,25 @@
         <v>54</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>5693</v>
+        <v>5694</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>5694</v>
+        <v>5695</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41461,25 +41484,25 @@
         <v>54</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41487,25 +41510,25 @@
         <v>54</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="102" x14ac:dyDescent="0.3">
@@ -41513,25 +41536,25 @@
         <v>54</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41539,25 +41562,25 @@
         <v>54</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41565,25 +41588,25 @@
         <v>54</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41591,25 +41614,25 @@
         <v>54</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41617,25 +41640,25 @@
         <v>54</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>5737</v>
+        <v>5738</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>5738</v>
+        <v>5739</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>5739</v>
+        <v>5740</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>5740</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41643,25 +41666,25 @@
         <v>55</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="127.5" x14ac:dyDescent="0.3">
@@ -41669,25 +41692,25 @@
         <v>55</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>5750</v>
+        <v>5751</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="153" x14ac:dyDescent="0.3">
@@ -41695,25 +41718,25 @@
         <v>55</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>5753</v>
+        <v>5754</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="140.25" x14ac:dyDescent="0.3">
@@ -41721,25 +41744,25 @@
         <v>55</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="178.5" x14ac:dyDescent="0.3">
@@ -41747,25 +41770,25 @@
         <v>55</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="89.25" x14ac:dyDescent="0.3">
@@ -41773,25 +41796,25 @@
         <v>55</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="51" x14ac:dyDescent="0.3">
@@ -41799,25 +41822,25 @@
         <v>55</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="165.75" x14ac:dyDescent="0.3">
@@ -41825,25 +41848,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -41851,25 +41874,25 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="102" x14ac:dyDescent="0.3">
@@ -41877,25 +41900,25 @@
         <v>55</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>4234</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="114.75" x14ac:dyDescent="0.3">
@@ -41903,25 +41926,25 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="127.5" x14ac:dyDescent="0.3">
@@ -41929,25 +41952,25 @@
         <v>55</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>4237</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="63.75" x14ac:dyDescent="0.3">
@@ -41955,25 +41978,25 @@
         <v>55</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="127.5" x14ac:dyDescent="0.3">
@@ -41981,25 +42004,25 @@
         <v>55</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="76.5" x14ac:dyDescent="0.3">
@@ -42007,25 +42030,25 @@
         <v>55</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>4240</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
     </row>
   </sheetData>
